--- a/output/pdf_financials_xlsx/BITK.xlsx
+++ b/output/pdf_financials_xlsx/BITK.xlsx
@@ -5679,10 +5679,10 @@
         <v>13.073908</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>13.134572</v>
+        <v>13.211301</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>13.134572</v>
+        <v>13.211301</v>
       </c>
     </row>
     <row r="93">
@@ -9218,7 +9218,11 @@
           <t>Warrants reserve (note 9)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10314,7 +10318,11 @@
           <t>Warrants reserve (note 9)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BITK.xlsx
+++ b/output/pdf_financials_xlsx/BITK.xlsx
@@ -2338,19 +2338,19 @@
         <v>3.656732</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.573813</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.044657</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.037707</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.125865</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.248512</v>
       </c>
     </row>
     <row r="35">
@@ -2446,19 +2446,19 @@
         <v>3.656732</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.573813</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.044657</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.037707</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.125865</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.248512</v>
       </c>
     </row>
     <row r="37">
@@ -3110,19 +3110,19 @@
         <v>0.09693</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.587552</v>
+        <v>0.013739</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.053478</v>
+        <v>0.008821000000000001</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.05456</v>
+        <v>0.016853</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.223083</v>
+        <v>0.097218</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.334913</v>
+        <v>0.08640100000000001</v>
       </c>
     </row>
     <row r="49">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
